--- a/VerveStacks_SVK_grids_kan/SuppXLS/Scen_Base_VS.xlsx
+++ b/VerveStacks_SVK_grids_kan/SuppXLS/Scen_Base_VS.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_SVK_grids_kan\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{E7CE514C-22DE-428D-99A8-7BB758C35388}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{D2765B3D-5FB6-4BC2-97DB-AA90B6CCC002}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1981,7 +1981,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5B2AB0C2-B182-4829-9EAE-E25239320550}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E8907768-98D1-4738-B11F-3B72CAC36924}">
   <dimension ref="B2:AF201"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -6414,7 +6414,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8AF197F7-EDFB-4150-94D7-3B63EFDECE8B}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D2305A46-F331-4C0A-860F-09AE9D6A010B}">
   <dimension ref="B9:L20"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
